--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N95_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.53218328090431</v>
+        <v>11.13647978314695</v>
       </c>
       <c r="D2" t="n">
-        <v>23.10367936065596</v>
+        <v>3.754347896106593</v>
       </c>
       <c r="E2" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F2" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.50259547677472</v>
+        <v>11.13167176497589</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2846843721875</v>
+        <v>2.32126121048047</v>
       </c>
       <c r="E3" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F3" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>69.20305267833204</v>
+        <v>11.24549606022896</v>
       </c>
       <c r="D4" t="n">
-        <v>45.43316536871303</v>
+        <v>7.382889372415868</v>
       </c>
       <c r="E4" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F4" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.67127876897051</v>
+        <v>10.99658279995771</v>
       </c>
       <c r="D5" t="n">
-        <v>27.42488431488982</v>
+        <v>4.456543701169596</v>
       </c>
       <c r="E5" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F5" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.13112572260903</v>
+        <v>9.446307929923968</v>
       </c>
       <c r="D6" t="n">
-        <v>45.62405571477913</v>
+        <v>7.413909053651608</v>
       </c>
       <c r="E6" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F6" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.89116464225033</v>
+        <v>11.84481425436568</v>
       </c>
       <c r="D7" t="n">
-        <v>72.4287279551769</v>
+        <v>11.76966829271625</v>
       </c>
       <c r="E7" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F7" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.72061437302688</v>
+        <v>10.19209983561687</v>
       </c>
       <c r="D8" t="n">
-        <v>59.56885357438284</v>
+        <v>9.679938705837211</v>
       </c>
       <c r="E8" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F8" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.76618181660877</v>
+        <v>8.249504545198926</v>
       </c>
       <c r="D9" t="n">
-        <v>13.0384048104053</v>
+        <v>2.118740781690861</v>
       </c>
       <c r="E9" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F9" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>62.22159007577442</v>
+        <v>10.11100838731334</v>
       </c>
       <c r="D10" t="n">
-        <v>22.80350850198276</v>
+        <v>3.705570131572198</v>
       </c>
       <c r="E10" t="n">
-        <v>6.432574613614475</v>
+        <v>1.045293374712352</v>
       </c>
       <c r="F10" t="n">
-        <v>19.6551538593732</v>
+        <v>3.193962502148145</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
